--- a/Design/Excel/ET/Datas/Game/Relic.xlsx
+++ b/Design/Excel/ET/Datas/Game/Relic.xlsx
@@ -570,17 +570,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>æµè¯éç©</t>
+          <t>测试遗物</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ManaBattery</t>
+          <t>法力电池</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>åå¡MPæ¶èåå°1ç¹</t>
+          <t>单卡MP消耗减少1点</t>
         </is>
       </c>
       <c r="F5" t="n">
